--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T21:42:02+08:00</t>
+    <t>2026-07-10T19:56:53+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T19:56:53+08:00</t>
+    <t>2026-07-10T21:30:50+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T21:30:50+08:00</t>
+    <t>2026-07-23T22:22:27+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T22:22:27+08:00</t>
+    <t>2026-07-24T13:54:16+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-24T13:54:16+08:00</t>
+    <t>2026-07-25T16:18:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-25T16:18:15+08:00</t>
+    <t>2026-07-26T10:07:44+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T10:07:44+08:00</t>
+    <t>2026-07-26T12:18:37+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="54">
   <si>
     <t>Property</t>
   </si>
@@ -54,13 +54,13 @@
     <t>Experimental</t>
   </si>
   <si>
-    <t>false</t>
+    <t>true</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T12:18:37+08:00</t>
+    <t>2026-07-26T14:28:30+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>依據勞工健康保護規則第 21 條規定，醫師依健康檢查結果判定之健康管理分級。</t>
+    <t>依據勞工健康保護規則第 21 條規定，醫師依健康檢查結果判定之健康管理分級。（**provisional**：本代碼系統為工作小組建議之本地代碼配置，**尚待勞動部職業安全衛生署確認官方代碼與定義（M-2）**；不得表述為已對接官方申報系統。）</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -97,9 +97,6 @@
   </si>
   <si>
     <t>Case Sensitive</t>
-  </si>
-  <si>
-    <t>true</t>
   </si>
   <si>
     <t>Value Set (all codes)</t>
@@ -439,53 +436,53 @@
         <v>27</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>33</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>34</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>36</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -500,72 +497,72 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="B1" t="s" s="1">
         <v>38</v>
       </c>
-      <c r="B1" t="s" s="1">
+      <c r="C1" t="s" s="1">
         <v>39</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>40</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>41</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>42</v>
       </c>
-      <c r="B2" t="s" s="2">
+      <c r="C2" t="s" s="2">
         <v>43</v>
       </c>
-      <c r="C2" t="s" s="2">
+      <c r="D2" t="s" s="2">
         <v>44</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="C3" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="C3" t="s" s="2">
+      <c r="D3" t="s" s="2">
         <v>47</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>48</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="C4" t="s" s="2">
         <v>49</v>
       </c>
-      <c r="C4" t="s" s="2">
+      <c r="D4" t="s" s="2">
         <v>50</v>
-      </c>
-      <c r="D4" t="s" s="2">
-        <v>51</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="C5" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="C5" t="s" s="2">
+      <c r="D5" t="s" s="2">
         <v>53</v>
-      </c>
-      <c r="D5" t="s" s="2">
-        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T14:28:30+08:00</t>
+    <t>2026-07-26T15:21:49+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T15:21:49+08:00</t>
+    <t>2026-07-26T16:11:18+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T16:11:18+08:00</t>
+    <t>2026-07-26T18:45:10+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T18:45:10+08:00</t>
+    <t>2026-07-29T09:46:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T09:46:30+00:00</t>
+    <t>2026-07-29T14:03:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T14:03:51+00:00</t>
+    <t>2026-07-29T16:26:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T16:26:07+00:00</t>
+    <t>2026-07-29T16:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T16:54:28+00:00</t>
+    <t>2026-07-30T07:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T07:25:13+00:00</t>
+    <t>2026-07-30T09:28:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T09:28:37+00:00</t>
+    <t>2026-07-30T10:44:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T10:44:37+00:00</t>
+    <t>2026-07-30T12:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:17:12+00:00</t>
+    <t>2026-07-30T14:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:17:56+00:00</t>
+    <t>2026-07-30T14:46:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:46:31+00:00</t>
+    <t>2026-08-05T16:28:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.2.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T16:28:11+00:00</t>
+    <t>2026-08-05T16:48:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.1</t>
+    <t>0.2.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T16:48:01+00:00</t>
+    <t>2026-08-17T03:02:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.3</t>
+    <t>0.2.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T03:02:16+00:00</t>
+    <t>2026-08-17T05:27:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.4</t>
+    <t>0.2.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T05:27:05+00:00</t>
+    <t>2026-08-17T06:57:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.5</t>
+    <t>0.3.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T06:57:01+00:00</t>
+    <t>2026-08-20T12:04:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T12:04:33+00:00</t>
+    <t>2026-08-20T13:40:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T13:40:11+00:00</t>
+    <t>2026-08-20T16:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>依據勞工健康保護規則第 21 條規定，醫師依健康檢查結果判定之健康管理分級。（**provisional**：本代碼系統為工作小組建議之本地代碼配置，**尚待勞動部職業安全衛生署確認官方代碼與定義（M-2）**；不得表述為已對接官方申報系統。）</t>
+    <t>【依據：勞工健康保護規則附表】依據勞工健康保護規則第 21 條規定，醫師依健康檢查結果判定之健康管理分級。（**provisional**：本代碼系統為工作小組建議之本地代碼配置，**尚待勞動部職業安全衛生署確認官方代碼與定義（M-2）**；不得表述為已對接官方申報系統。）</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T16:35:38+00:00</t>
+    <t>2026-08-20T17:39:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T17:39:23+00:00</t>
+    <t>2026-08-20T18:13:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.1</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T18:13:29+00:00</t>
+    <t>2026-08-21T00:14:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T00:14:56+00:00</t>
+    <t>2026-08-21T00:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.7.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T00:59:40+00:00</t>
+    <t>2026-08-21T01:22:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.1</t>
+    <t>0.8.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T01:22:55+00:00</t>
+    <t>2026-08-21T04:20:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.1</t>
+    <t>0.8.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T04:20:36+00:00</t>
+    <t>2026-08-21T12:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.5</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T12:32:47+00:00</t>
+    <t>2026-08-21T14:27:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T14:27:31+00:00</t>
+    <t>2026-08-21T15:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.2</t>
+    <t>0.9.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T15:06:05+00:00</t>
+    <t>2026-08-21T16:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.3</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T16:05:47+00:00</t>
+    <t>2026-08-22T02:14:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T02:14:01+00:00</t>
+    <t>2026-08-22T04:25:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.10.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T04:25:10+00:00</t>
+    <t>2026-08-22T08:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.1</t>
+    <t>0.10.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T08:31:54+00:00</t>
+    <t>2026-08-22T14:05:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-HealthMgmtLevel.xlsx
+++ b/CodeSystem-CS-HealthMgmtLevel.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.2</t>
+    <t>0.10.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T14:05:28+00:00</t>
+    <t>2026-08-22T17:09:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
